--- a/RESULTS/tables/internal_cv_fold_metrics.xlsx
+++ b/RESULTS/tables/internal_cv_fold_metrics.xlsx
@@ -512,46 +512,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.8443840200794813</v>
+        <v>0.8577703409328592</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7472178060413355</v>
+        <v>0.7713458755426917</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4454976303317535</v>
+        <v>0.5052132701421801</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4454976303317535</v>
+        <v>0.5052132701421801</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9573268921095008</v>
+        <v>0.9575952764358562</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7472178060413355</v>
+        <v>0.7713458755426917</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8591040462427746</v>
+        <v>0.8723716381418093</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5581947743467933</v>
+        <v>0.6105383734249714</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8699413370372915</v>
+        <v>0.8855680462384219</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1106262598874371</v>
+        <v>0.1026124733906017</v>
       </c>
       <c r="K2" t="n">
-        <v>470</v>
+        <v>533</v>
       </c>
       <c r="L2" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M2" t="n">
-        <v>3567</v>
+        <v>3568</v>
       </c>
       <c r="N2" t="n">
-        <v>585</v>
+        <v>522</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -564,46 +564,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.856694560669456</v>
+        <v>0.8667364016736402</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8019639934533551</v>
+        <v>0.7924263674614306</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4648956356736243</v>
+        <v>0.5360531309297912</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4648956356736243</v>
+        <v>0.5360531309297912</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9675254965110037</v>
+        <v>0.9602791196994096</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8019639934533551</v>
+        <v>0.7924263674614306</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8647157591748621</v>
+        <v>0.8797639537742808</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5885885885885885</v>
+        <v>0.6395019807583475</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8854587131200722</v>
+        <v>0.8942624319999675</v>
       </c>
       <c r="J3" t="n">
-        <v>0.10495726854009</v>
+        <v>0.09843795303384327</v>
       </c>
       <c r="K3" t="n">
-        <v>490</v>
+        <v>565</v>
       </c>
       <c r="L3" t="n">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="M3" t="n">
-        <v>3605</v>
+        <v>3578</v>
       </c>
       <c r="N3" t="n">
-        <v>564</v>
+        <v>489</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -616,46 +616,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.847907949790795</v>
+        <v>0.8742677824267783</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7738693467336684</v>
+        <v>0.8106995884773662</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4383301707779886</v>
+        <v>0.5607210626185958</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4383301707779886</v>
+        <v>0.5607210626185958</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9637681159420289</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7738693467336684</v>
+        <v>0.8106995884773662</v>
       </c>
       <c r="G4" t="n">
-        <v>0.858474778866842</v>
+        <v>0.8857072327820291</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5596608116293156</v>
+        <v>0.6629276500280427</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8745189962120633</v>
+        <v>0.8870728385894902</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1090579037426073</v>
+        <v>0.09934664459325344</v>
       </c>
       <c r="K4" t="n">
-        <v>462</v>
+        <v>591</v>
       </c>
       <c r="L4" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M4" t="n">
-        <v>3591</v>
+        <v>3588</v>
       </c>
       <c r="N4" t="n">
-        <v>592</v>
+        <v>463</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -668,46 +668,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.849163179916318</v>
+        <v>0.8631799163179916</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7630331753554502</v>
+        <v>0.7645502645502645</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4582542694497154</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4582542694497154</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9597423510466989</v>
+        <v>0.9522275899087493</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7630331753554502</v>
+        <v>0.7645502645502645</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8623101036894141</v>
+        <v>0.8817097415506958</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5726141078838174</v>
+        <v>0.6386740331491713</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8682809703799446</v>
+        <v>0.8844387762896961</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1105097104734056</v>
+        <v>0.1014637499252328</v>
       </c>
       <c r="K5" t="n">
-        <v>483</v>
+        <v>578</v>
       </c>
       <c r="L5" t="n">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="M5" t="n">
-        <v>3576</v>
+        <v>3548</v>
       </c>
       <c r="N5" t="n">
-        <v>571</v>
+        <v>476</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -720,46 +720,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.8514644351464435</v>
+        <v>0.8667364016736402</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7851239669421488</v>
+        <v>0.8002873563218391</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4502369668246445</v>
+        <v>0.5279620853080569</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4502369668246445</v>
+        <v>0.5279620853080569</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9651006711409396</v>
+        <v>0.9626845637583893</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7851239669421488</v>
+        <v>0.8002873563218391</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8610778443113772</v>
+        <v>0.8780607247796278</v>
       </c>
       <c r="H6" t="n">
-        <v>0.572289156626506</v>
+        <v>0.6362078812107367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8781471420846718</v>
+        <v>0.8883243105696745</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1076139703848251</v>
+        <v>0.1008183744847071</v>
       </c>
       <c r="K6" t="n">
-        <v>475</v>
+        <v>557</v>
       </c>
       <c r="L6" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="M6" t="n">
-        <v>3595</v>
+        <v>3586</v>
       </c>
       <c r="N6" t="n">
-        <v>580</v>
+        <v>498</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -772,46 +772,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.7889562852959632</v>
+        <v>0.8343442794394478</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5653409090909091</v>
+        <v>0.681881051175657</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1886255924170616</v>
+        <v>0.4672985781990521</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1886255924170616</v>
+        <v>0.4672985781990521</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9589371980676329</v>
+        <v>0.9382716049382716</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5653409090909091</v>
+        <v>0.681881051175657</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8067283811244074</v>
+        <v>0.8615081320847708</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2828713574982232</v>
+        <v>0.5545556805399325</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7854408498752204</v>
+        <v>0.8529999262261094</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1427142562322732</v>
+        <v>0.1172018836404627</v>
       </c>
       <c r="K7" t="n">
-        <v>199</v>
+        <v>493</v>
       </c>
       <c r="L7" t="n">
-        <v>153</v>
+        <v>230</v>
       </c>
       <c r="M7" t="n">
-        <v>3573</v>
+        <v>3496</v>
       </c>
       <c r="N7" t="n">
-        <v>856</v>
+        <v>562</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -824,46 +824,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.7949790794979079</v>
+        <v>0.8435146443514644</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5973684210526315</v>
+        <v>0.713091922005571</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2153700189753321</v>
+        <v>0.4857685009487666</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2153700189753321</v>
+        <v>0.4857685009487666</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9589371980676329</v>
+        <v>0.9447128287707998</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5973684210526315</v>
+        <v>0.713091922005571</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8120454545454545</v>
+        <v>0.8665681930083703</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3165969316596932</v>
+        <v>0.5778781038374717</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8042170714839362</v>
+        <v>0.8626717634225266</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1380798163124984</v>
+        <v>0.1131979235773683</v>
       </c>
       <c r="K8" t="n">
-        <v>227</v>
+        <v>512</v>
       </c>
       <c r="L8" t="n">
-        <v>153</v>
+        <v>206</v>
       </c>
       <c r="M8" t="n">
-        <v>3573</v>
+        <v>3520</v>
       </c>
       <c r="N8" t="n">
-        <v>827</v>
+        <v>542</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -876,46 +876,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.792468619246862</v>
+        <v>0.8460251046025105</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5815789473684211</v>
+        <v>0.7103174603174603</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.5094876660341556</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.5094876660341556</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9573268921095008</v>
+        <v>0.9412238325281803</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5815789473684211</v>
+        <v>0.7103174603174603</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8106818181818182</v>
+        <v>0.8715208747514911</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3082287308228731</v>
+        <v>0.5933701657458563</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7958244593354458</v>
+        <v>0.8536621728843217</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1403008085290128</v>
+        <v>0.1150012531111617</v>
       </c>
       <c r="K9" t="n">
-        <v>221</v>
+        <v>537</v>
       </c>
       <c r="L9" t="n">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="M9" t="n">
-        <v>3567</v>
+        <v>3507</v>
       </c>
       <c r="N9" t="n">
-        <v>833</v>
+        <v>517</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -928,46 +928,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.7964435146443515</v>
+        <v>0.8416317991631799</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5995085995085995</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2314990512333966</v>
+        <v>0.5009487666034156</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2314990512333966</v>
+        <v>0.5009487666034156</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9562533548040795</v>
+        <v>0.9380032206119162</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5995085995085995</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8147724674136748</v>
+        <v>0.8691867694603332</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3340177960301163</v>
+        <v>0.5824600110314396</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7861528201743531</v>
+        <v>0.8559659747749289</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1424864912976685</v>
+        <v>0.1155427984056087</v>
       </c>
       <c r="K10" t="n">
-        <v>244</v>
+        <v>528</v>
       </c>
       <c r="L10" t="n">
-        <v>163</v>
+        <v>231</v>
       </c>
       <c r="M10" t="n">
-        <v>3563</v>
+        <v>3495</v>
       </c>
       <c r="N10" t="n">
-        <v>810</v>
+        <v>526</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -980,46 +980,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.7874476987447698</v>
+        <v>0.8389121338912134</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6917900403768507</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1725118483412322</v>
+        <v>0.4872037914691943</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1725118483412322</v>
+        <v>0.4872037914691943</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9616107382550335</v>
+        <v>0.9385234899328859</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6917900403768507</v>
       </c>
       <c r="G11" t="n">
-        <v>0.804040404040404</v>
+        <v>0.8659895962348279</v>
       </c>
       <c r="H11" t="n">
-        <v>0.263768115942029</v>
+        <v>0.5717463848720801</v>
       </c>
       <c r="I11" t="n">
-        <v>0.803349088711473</v>
+        <v>0.8602036960463119</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1397172658857278</v>
+        <v>0.1167256531419186</v>
       </c>
       <c r="K11" t="n">
-        <v>182</v>
+        <v>514</v>
       </c>
       <c r="L11" t="n">
-        <v>143</v>
+        <v>229</v>
       </c>
       <c r="M11" t="n">
-        <v>3582</v>
+        <v>3496</v>
       </c>
       <c r="N11" t="n">
-        <v>873</v>
+        <v>541</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1032,46 +1032,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.8519138255595063</v>
+        <v>0.8548420832461828</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7839607201309329</v>
+        <v>0.7658321060382917</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4540284360189574</v>
+        <v>0.4928909952606635</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4540284360189574</v>
+        <v>0.4928909952606635</v>
       </c>
       <c r="E12" t="n">
-        <v>0.964573268921095</v>
+        <v>0.9573268921095008</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7839607201309329</v>
+        <v>0.7658321060382917</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8618705035971223</v>
+        <v>0.8695758166747928</v>
       </c>
       <c r="H12" t="n">
-        <v>0.575030012004802</v>
+        <v>0.5997693194925029</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8703497645595317</v>
+        <v>0.8853457069955455</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1118305154958735</v>
+        <v>0.1050662943601993</v>
       </c>
       <c r="K12" t="n">
-        <v>479</v>
+        <v>520</v>
       </c>
       <c r="L12" t="n">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="M12" t="n">
-        <v>3594</v>
+        <v>3567</v>
       </c>
       <c r="N12" t="n">
-        <v>576</v>
+        <v>535</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1084,46 +1084,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.8594142259414226</v>
+        <v>0.8656903765690377</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8131147540983606</v>
+        <v>0.7968299711815562</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.5246679316888045</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.5246679316888045</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9694041867954911</v>
+        <v>0.962157809983897</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8131147540983606</v>
+        <v>0.7968299711815562</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8661870503597122</v>
+        <v>0.8773861967694567</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5961538461538461</v>
+        <v>0.6327231121281465</v>
       </c>
       <c r="I13" t="n">
-        <v>0.885553691634048</v>
+        <v>0.8935890521602647</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1059143533516159</v>
+        <v>0.1008975506100422</v>
       </c>
       <c r="K13" t="n">
-        <v>496</v>
+        <v>553</v>
       </c>
       <c r="L13" t="n">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="M13" t="n">
-        <v>3612</v>
+        <v>3585</v>
       </c>
       <c r="N13" t="n">
-        <v>558</v>
+        <v>501</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1136,46 +1136,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.850836820083682</v>
+        <v>0.8696652719665272</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7884940778341794</v>
+        <v>0.8100719424460432</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4421252371916509</v>
+        <v>0.5341555977229602</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4421252371916509</v>
+        <v>0.5341555977229602</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9664519592055824</v>
+        <v>0.964573268921095</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7884940778341794</v>
+        <v>0.8100719424460432</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8596323704941513</v>
+        <v>0.8798041615667075</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5665653495440729</v>
+        <v>0.6437964551172098</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8734029350143258</v>
+        <v>0.8856835550177683</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1108067533959493</v>
+        <v>0.1019080497634884</v>
       </c>
       <c r="K14" t="n">
-        <v>466</v>
+        <v>563</v>
       </c>
       <c r="L14" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="M14" t="n">
-        <v>3601</v>
+        <v>3594</v>
       </c>
       <c r="N14" t="n">
-        <v>588</v>
+        <v>491</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1188,46 +1188,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.8531380753138076</v>
+        <v>0.8596234309623431</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7767295597484277</v>
+        <v>0.780380673499268</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4686907020872865</v>
+        <v>0.5056925996204934</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4686907020872865</v>
+        <v>0.5056925996204934</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9618894256575417</v>
+        <v>0.9597423510466989</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7767295597484277</v>
+        <v>0.780380673499268</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8648648648648649</v>
+        <v>0.8728337808152307</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5846153846153846</v>
+        <v>0.6137017846862406</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8676698485742019</v>
+        <v>0.878601926459639</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1117996683954732</v>
+        <v>0.1046144759549754</v>
       </c>
       <c r="K15" t="n">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="L15" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="M15" t="n">
-        <v>3584</v>
+        <v>3576</v>
       </c>
       <c r="N15" t="n">
-        <v>560</v>
+        <v>521</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1240,46 +1240,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.8518828451882845</v>
+        <v>0.8604602510460251</v>
       </c>
       <c r="B16" t="n">
-        <v>0.7848932676518884</v>
+        <v>0.8012422360248447</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4530805687203792</v>
+        <v>0.4890995260663507</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4530805687203792</v>
+        <v>0.4890995260663507</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9648322147651007</v>
+        <v>0.9656375838926174</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7848932676518884</v>
+        <v>0.8012422360248447</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8616638695756413</v>
+        <v>0.8696808510638298</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5745192307692307</v>
+        <v>0.607416127133608</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8753200801552211</v>
+        <v>0.8815447056204078</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1093884191692633</v>
+        <v>0.1047366735752774</v>
       </c>
       <c r="K16" t="n">
-        <v>478</v>
+        <v>516</v>
       </c>
       <c r="L16" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="M16" t="n">
-        <v>3594</v>
+        <v>3597</v>
       </c>
       <c r="N16" t="n">
-        <v>577</v>
+        <v>539</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1292,46 +1292,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.8456389876594854</v>
+        <v>0.8542145994561807</v>
       </c>
       <c r="B17" t="n">
-        <v>0.7139001349527665</v>
+        <v>0.7342931937172775</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5014218009478673</v>
+        <v>0.5317535545023697</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5014218009478673</v>
+        <v>0.5317535545023697</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9431025228126677</v>
+        <v>0.9455179817498658</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7139001349527665</v>
+        <v>0.7342931937172775</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8698019801980198</v>
+        <v>0.8770226537216829</v>
       </c>
       <c r="H17" t="n">
-        <v>0.589086859688196</v>
+        <v>0.616822429906542</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8519237177970609</v>
+        <v>0.8657968979350942</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1154350107692038</v>
+        <v>0.1082724980455786</v>
       </c>
       <c r="K17" t="n">
-        <v>529</v>
+        <v>561</v>
       </c>
       <c r="L17" t="n">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="M17" t="n">
-        <v>3514</v>
+        <v>3523</v>
       </c>
       <c r="N17" t="n">
-        <v>526</v>
+        <v>494</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1344,46 +1344,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.852510460251046</v>
+        <v>0.8663179916317991</v>
       </c>
       <c r="B18" t="n">
-        <v>0.7367706919945726</v>
+        <v>0.7807848443843031</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5151802656546489</v>
+        <v>0.547438330170778</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5151802656546489</v>
+        <v>0.547438330170778</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9479334406870639</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7367706919945726</v>
+        <v>0.7807848443843031</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8736087064061341</v>
+        <v>0.8819599109131403</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6063651591289783</v>
+        <v>0.6436140546569994</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8739004900178344</v>
+        <v>0.8836420262354593</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1075655438963767</v>
+        <v>0.1012457629707607</v>
       </c>
       <c r="K18" t="n">
-        <v>543</v>
+        <v>577</v>
       </c>
       <c r="L18" t="n">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="M18" t="n">
-        <v>3532</v>
+        <v>3564</v>
       </c>
       <c r="N18" t="n">
-        <v>511</v>
+        <v>477</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1396,46 +1396,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.8433054393305439</v>
+        <v>0.8631799163179916</v>
       </c>
       <c r="B19" t="n">
-        <v>0.7163120567375887</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4791271347248577</v>
+        <v>0.5540796963946869</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4791271347248577</v>
+        <v>0.5540796963946869</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9463231347289318</v>
+        <v>0.9506172839506173</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7163120567375887</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8652760736196319</v>
+        <v>0.882851445663011</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5741898806139852</v>
+        <v>0.6410537870472008</v>
       </c>
       <c r="I19" t="n">
-        <v>0.851421265612889</v>
+        <v>0.8730861702116826</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1155427513491867</v>
+        <v>0.1040304220749578</v>
       </c>
       <c r="K19" t="n">
-        <v>505</v>
+        <v>584</v>
       </c>
       <c r="L19" t="n">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="M19" t="n">
-        <v>3526</v>
+        <v>3542</v>
       </c>
       <c r="N19" t="n">
-        <v>549</v>
+        <v>470</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1448,46 +1448,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.8387029288702929</v>
+        <v>0.8531380753138076</v>
       </c>
       <c r="B20" t="n">
-        <v>0.6849673202614379</v>
+        <v>0.7328042328042328</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4971537001897533</v>
+        <v>0.5256166982922201</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4971537001897533</v>
+        <v>0.5256166982922201</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9353193773483629</v>
+        <v>0.9457863660762211</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6849673202614379</v>
+        <v>0.7328042328042328</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8679950186799502</v>
+        <v>0.8757455268389662</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5761407366684992</v>
+        <v>0.6121546961325967</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8500276532617097</v>
+        <v>0.8615557022247889</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1168005196985145</v>
+        <v>0.1094110121589448</v>
       </c>
       <c r="K20" t="n">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="L20" t="n">
-        <v>241</v>
+        <v>202</v>
       </c>
       <c r="M20" t="n">
-        <v>3485</v>
+        <v>3524</v>
       </c>
       <c r="N20" t="n">
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1500,37 +1500,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.8481171548117155</v>
+        <v>0.8531380753138076</v>
       </c>
       <c r="B21" t="n">
-        <v>0.7275242047026279</v>
+        <v>0.7362784471218207</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4985781990521327</v>
+        <v>0.5213270142180095</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4985781990521327</v>
+        <v>0.5213270142180095</v>
       </c>
       <c r="E21" t="n">
         <v>0.9471140939597316</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7275242047026279</v>
+        <v>0.7362784471218207</v>
       </c>
       <c r="G21" t="n">
-        <v>0.869608084791718</v>
+        <v>0.8747830399206546</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5916760404949382</v>
+        <v>0.6104328523862376</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8572721778682527</v>
+        <v>0.8693113648652946</v>
       </c>
       <c r="J21" t="n">
-        <v>0.112798701073398</v>
+        <v>0.1067589144638376</v>
       </c>
       <c r="K21" t="n">
-        <v>526</v>
+        <v>550</v>
       </c>
       <c r="L21" t="n">
         <v>197</v>
@@ -1539,7 +1539,7 @@
         <v>3528</v>
       </c>
       <c r="N21" t="n">
-        <v>529</v>
+        <v>505</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1552,46 +1552,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.7893746078226312</v>
+        <v>0.8343442794394478</v>
       </c>
       <c r="B22" t="n">
-        <v>0.5641711229946524</v>
+        <v>0.681881051175657</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2</v>
+        <v>0.4672985781990521</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2</v>
+        <v>0.4672985781990521</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9562533548040795</v>
+        <v>0.9382716049382716</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5641711229946524</v>
+        <v>0.681881051175657</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8084864987519855</v>
+        <v>0.8615081320847708</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2953114065780266</v>
+        <v>0.5545556805399325</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7906083293266479</v>
+        <v>0.8529999262261094</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1413440071558398</v>
+        <v>0.1172018836404627</v>
       </c>
       <c r="K22" t="n">
-        <v>211</v>
+        <v>493</v>
       </c>
       <c r="L22" t="n">
-        <v>163</v>
+        <v>230</v>
       </c>
       <c r="M22" t="n">
-        <v>3563</v>
+        <v>3496</v>
       </c>
       <c r="N22" t="n">
-        <v>844</v>
+        <v>562</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1604,46 +1604,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.7958158995815899</v>
+        <v>0.8435146443514644</v>
       </c>
       <c r="B23" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.713091922005571</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.4857685009487666</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.4857685009487666</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9616210413311863</v>
+        <v>0.9447128287707998</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.713091922005571</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8113677536231884</v>
+        <v>0.8665681930083703</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3117066290550071</v>
+        <v>0.5778781038374717</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8054207268071636</v>
+        <v>0.8626717634225266</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1380501224394543</v>
+        <v>0.1131979235773683</v>
       </c>
       <c r="K23" t="n">
-        <v>221</v>
+        <v>512</v>
       </c>
       <c r="L23" t="n">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="M23" t="n">
-        <v>3583</v>
+        <v>3520</v>
       </c>
       <c r="N23" t="n">
-        <v>833</v>
+        <v>542</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1656,46 +1656,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.7912133891213389</v>
+        <v>0.8460251046025105</v>
       </c>
       <c r="B24" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.7103174603174603</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1992409867172676</v>
+        <v>0.5094876660341556</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1992409867172676</v>
+        <v>0.5094876660341556</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9586688137412775</v>
+        <v>0.9412238325281803</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.7103174603174603</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8088768115942029</v>
+        <v>0.8715208747514911</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2961918194640338</v>
+        <v>0.5933701657458563</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7958583256688474</v>
+        <v>0.8536621728843217</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1403685139852771</v>
+        <v>0.1150012531111617</v>
       </c>
       <c r="K24" t="n">
-        <v>210</v>
+        <v>537</v>
       </c>
       <c r="L24" t="n">
-        <v>154</v>
+        <v>219</v>
       </c>
       <c r="M24" t="n">
-        <v>3572</v>
+        <v>3507</v>
       </c>
       <c r="N24" t="n">
-        <v>844</v>
+        <v>517</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1708,46 +1708,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.7972803347280335</v>
+        <v>0.8416317991631799</v>
       </c>
       <c r="B25" t="n">
-        <v>0.6115485564304461</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2210626185958254</v>
+        <v>0.5009487666034156</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2210626185958254</v>
+        <v>0.5009487666034156</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9602791196994096</v>
+        <v>0.9380032206119162</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6115485564304461</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8133666742441464</v>
+        <v>0.8691867694603332</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3247386759581882</v>
+        <v>0.5824600110314396</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7872301769910602</v>
+        <v>0.8559659747749289</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1420615150231345</v>
+        <v>0.1155427984056087</v>
       </c>
       <c r="K25" t="n">
-        <v>233</v>
+        <v>528</v>
       </c>
       <c r="L25" t="n">
-        <v>148</v>
+        <v>231</v>
       </c>
       <c r="M25" t="n">
-        <v>3578</v>
+        <v>3495</v>
       </c>
       <c r="N25" t="n">
-        <v>821</v>
+        <v>526</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1760,46 +1760,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.7861924686192469</v>
+        <v>0.8389121338912134</v>
       </c>
       <c r="B26" t="n">
-        <v>0.5437665782493368</v>
+        <v>0.6917900403768507</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1943127962085308</v>
+        <v>0.4872037914691943</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1943127962085308</v>
+        <v>0.4872037914691943</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9538255033557047</v>
+        <v>0.9385234899328859</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5437665782493368</v>
+        <v>0.6917900403768507</v>
       </c>
       <c r="G26" t="n">
-        <v>0.806949806949807</v>
+        <v>0.8659895962348279</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2863128491620112</v>
+        <v>0.5717463848720801</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8049509208308152</v>
+        <v>0.8602036960463119</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1389440033873684</v>
+        <v>0.1167256531419186</v>
       </c>
       <c r="K26" t="n">
-        <v>205</v>
+        <v>514</v>
       </c>
       <c r="L26" t="n">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="M26" t="n">
-        <v>3553</v>
+        <v>3496</v>
       </c>
       <c r="N26" t="n">
-        <v>850</v>
+        <v>541</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1812,46 +1812,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.7900020916126334</v>
+        <v>0.835808408282786</v>
       </c>
       <c r="B27" t="n">
-        <v>0.5702479338842975</v>
+        <v>0.6928571428571428</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1962085308056872</v>
+        <v>0.4597156398104265</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1962085308056872</v>
+        <v>0.4597156398104265</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9581320450885669</v>
+        <v>0.9422973698336017</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5702479338842975</v>
+        <v>0.6928571428571428</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8080579447713898</v>
+        <v>0.8603283508943886</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2919605077574048</v>
+        <v>0.5527065527065527</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7882312836911368</v>
+        <v>0.8493224249732252</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1417804776925506</v>
+        <v>0.1181822722361692</v>
       </c>
       <c r="K27" t="n">
-        <v>207</v>
+        <v>485</v>
       </c>
       <c r="L27" t="n">
-        <v>156</v>
+        <v>215</v>
       </c>
       <c r="M27" t="n">
-        <v>3570</v>
+        <v>3511</v>
       </c>
       <c r="N27" t="n">
-        <v>848</v>
+        <v>570</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -1864,46 +1864,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.7949790794979079</v>
+        <v>0.843723849372385</v>
       </c>
       <c r="B28" t="n">
-        <v>0.6022099447513812</v>
+        <v>0.7195994277539342</v>
       </c>
       <c r="C28" t="n">
-        <v>0.206831119544592</v>
+        <v>0.4772296015180266</v>
       </c>
       <c r="D28" t="n">
-        <v>0.206831119544592</v>
+        <v>0.4772296015180266</v>
       </c>
       <c r="E28" t="n">
-        <v>0.961352657004831</v>
+        <v>0.9473966720343532</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6022099447513812</v>
+        <v>0.7195994277539342</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8107741059302852</v>
+        <v>0.8649840725312423</v>
       </c>
       <c r="H28" t="n">
-        <v>0.307909604519774</v>
+        <v>0.5738733599543639</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8048816664476813</v>
+        <v>0.8624013420234853</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1384447277380826</v>
+        <v>0.1138434331412837</v>
       </c>
       <c r="K28" t="n">
-        <v>218</v>
+        <v>503</v>
       </c>
       <c r="L28" t="n">
-        <v>144</v>
+        <v>196</v>
       </c>
       <c r="M28" t="n">
-        <v>3582</v>
+        <v>3530</v>
       </c>
       <c r="N28" t="n">
-        <v>836</v>
+        <v>551</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -1916,46 +1916,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.793305439330544</v>
+        <v>0.84581589958159</v>
       </c>
       <c r="B29" t="n">
-        <v>0.59375</v>
+        <v>0.7139001349527665</v>
       </c>
       <c r="C29" t="n">
-        <v>0.198292220113852</v>
+        <v>0.5018975332068312</v>
       </c>
       <c r="D29" t="n">
-        <v>0.198292220113852</v>
+        <v>0.5018975332068312</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9616210413311863</v>
+        <v>0.9431025228126677</v>
       </c>
       <c r="F29" t="n">
-        <v>0.59375</v>
+        <v>0.7139001349527665</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8091689250225835</v>
+        <v>0.8700173310225303</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2972972972972973</v>
+        <v>0.5894150417827299</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7952184302114177</v>
+        <v>0.8515479460705377</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1405796552297682</v>
+        <v>0.1158982461150199</v>
       </c>
       <c r="K29" t="n">
-        <v>209</v>
+        <v>529</v>
       </c>
       <c r="L29" t="n">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="M29" t="n">
-        <v>3583</v>
+        <v>3514</v>
       </c>
       <c r="N29" t="n">
-        <v>845</v>
+        <v>525</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -1968,46 +1968,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.797071129707113</v>
+        <v>0.8412133891213389</v>
       </c>
       <c r="B30" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.7006802721088435</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2191650853889943</v>
+        <v>0.4886148007590133</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2191650853889943</v>
+        <v>0.4886148007590133</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9605475040257649</v>
+        <v>0.940955448201825</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.7006802721088435</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8130395274875056</v>
+        <v>0.8667490729295426</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3226256983240223</v>
+        <v>0.5757406372275014</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7856389685893578</v>
+        <v>0.8527810116306664</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1424212180516005</v>
+        <v>0.1165569484402106</v>
       </c>
       <c r="K30" t="n">
-        <v>231</v>
+        <v>515</v>
       </c>
       <c r="L30" t="n">
-        <v>147</v>
+        <v>220</v>
       </c>
       <c r="M30" t="n">
-        <v>3579</v>
+        <v>3506</v>
       </c>
       <c r="N30" t="n">
-        <v>823</v>
+        <v>539</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2020,46 +2020,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.7853556485355648</v>
+        <v>0.8391213389121339</v>
       </c>
       <c r="B31" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.692722371967655</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1924170616113744</v>
+        <v>0.4872037914691943</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1924170616113744</v>
+        <v>0.4872037914691943</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9532885906040268</v>
+        <v>0.9387919463087249</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.692722371967655</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8064955712014535</v>
+        <v>0.866022783556216</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2835195530726257</v>
+        <v>0.572064552031163</v>
       </c>
       <c r="I31" t="n">
-        <v>0.804622157193295</v>
+        <v>0.8602573873214797</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1390712337235988</v>
+        <v>0.1166675693437824</v>
       </c>
       <c r="K31" t="n">
-        <v>203</v>
+        <v>514</v>
       </c>
       <c r="L31" t="n">
-        <v>174</v>
+        <v>228</v>
       </c>
       <c r="M31" t="n">
-        <v>3551</v>
+        <v>3497</v>
       </c>
       <c r="N31" t="n">
-        <v>852</v>
+        <v>541</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2072,46 +2072,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.7897929303492993</v>
+        <v>0.835599247019452</v>
       </c>
       <c r="B32" t="n">
-        <v>0.569060773480663</v>
+        <v>0.689703808180536</v>
       </c>
       <c r="C32" t="n">
-        <v>0.195260663507109</v>
+        <v>0.4635071090047393</v>
       </c>
       <c r="D32" t="n">
-        <v>0.195260663507109</v>
+        <v>0.4635071090047393</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9581320450885669</v>
+        <v>0.940955448201825</v>
       </c>
       <c r="F32" t="n">
-        <v>0.569060773480663</v>
+        <v>0.689703808180536</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8078750848608283</v>
+        <v>0.8610019646365422</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2907551164431899</v>
+        <v>0.5544217687074829</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7881847298222049</v>
+        <v>0.8499174495602821</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1417847657708682</v>
+        <v>0.1178826463053576</v>
       </c>
       <c r="K32" t="n">
-        <v>206</v>
+        <v>489</v>
       </c>
       <c r="L32" t="n">
-        <v>156</v>
+        <v>220</v>
       </c>
       <c r="M32" t="n">
-        <v>3570</v>
+        <v>3506</v>
       </c>
       <c r="N32" t="n">
-        <v>849</v>
+        <v>566</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2124,46 +2124,46 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.7949790794979079</v>
+        <v>0.8439330543933055</v>
       </c>
       <c r="B33" t="n">
-        <v>0.6022099447513812</v>
+        <v>0.7181303116147308</v>
       </c>
       <c r="C33" t="n">
-        <v>0.206831119544592</v>
+        <v>0.4810246679316888</v>
       </c>
       <c r="D33" t="n">
-        <v>0.206831119544592</v>
+        <v>0.4810246679316888</v>
       </c>
       <c r="E33" t="n">
-        <v>0.961352657004831</v>
+        <v>0.9465915190552872</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6022099447513812</v>
+        <v>0.7181303116147308</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8107741059302852</v>
+        <v>0.8657339224349534</v>
       </c>
       <c r="H33" t="n">
-        <v>0.307909604519774</v>
+        <v>0.5761363636363637</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8048539113323372</v>
+        <v>0.8630022784657991</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1384644789018589</v>
+        <v>0.1135131156606892</v>
       </c>
       <c r="K33" t="n">
-        <v>218</v>
+        <v>507</v>
       </c>
       <c r="L33" t="n">
-        <v>144</v>
+        <v>199</v>
       </c>
       <c r="M33" t="n">
-        <v>3582</v>
+        <v>3527</v>
       </c>
       <c r="N33" t="n">
-        <v>836</v>
+        <v>547</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2176,46 +2176,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.793305439330544</v>
+        <v>0.8462343096234309</v>
       </c>
       <c r="B34" t="n">
-        <v>0.5942857142857143</v>
+        <v>0.7123834886817576</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1973434535104364</v>
+        <v>0.5075901328273245</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1973434535104364</v>
+        <v>0.5075901328273245</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9618894256575417</v>
+        <v>0.9420289855072463</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5942857142857143</v>
+        <v>0.7123834886817576</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8090293453724605</v>
+        <v>0.8711839166046166</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.592797783933518</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7951886380233877</v>
+        <v>0.8520419361968464</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1405952029363767</v>
+        <v>0.1156194259539978</v>
       </c>
       <c r="K34" t="n">
-        <v>208</v>
+        <v>535</v>
       </c>
       <c r="L34" t="n">
-        <v>142</v>
+        <v>216</v>
       </c>
       <c r="M34" t="n">
-        <v>3584</v>
+        <v>3510</v>
       </c>
       <c r="N34" t="n">
-        <v>846</v>
+        <v>519</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2228,46 +2228,46 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.796652719665272</v>
+        <v>0.8414225941422594</v>
       </c>
       <c r="B35" t="n">
-        <v>0.6090425531914894</v>
+        <v>0.6994609164420486</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2172675521821632</v>
+        <v>0.4924098671726755</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2172675521821632</v>
+        <v>0.4924098671726755</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9605475040257649</v>
+        <v>0.9401502952227589</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6090425531914894</v>
+        <v>0.6994609164420486</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8126702997275205</v>
+        <v>0.8675086676572561</v>
       </c>
       <c r="H35" t="n">
-        <v>0.3202797202797203</v>
+        <v>0.5779510022271714</v>
       </c>
       <c r="I35" t="n">
-        <v>0.785529985200667</v>
+        <v>0.853493732436614</v>
       </c>
       <c r="J35" t="n">
-        <v>0.1424444215707613</v>
+        <v>0.1162202529716753</v>
       </c>
       <c r="K35" t="n">
-        <v>229</v>
+        <v>519</v>
       </c>
       <c r="L35" t="n">
-        <v>147</v>
+        <v>223</v>
       </c>
       <c r="M35" t="n">
-        <v>3579</v>
+        <v>3503</v>
       </c>
       <c r="N35" t="n">
-        <v>825</v>
+        <v>535</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2280,46 +2280,46 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.7857740585774059</v>
+        <v>0.8376569037656904</v>
       </c>
       <c r="B36" t="n">
-        <v>0.5411140583554377</v>
+        <v>0.683311432325887</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1933649289099526</v>
+        <v>0.4928909952606635</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1933649289099526</v>
+        <v>0.4928909952606635</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9535570469798658</v>
+        <v>0.9353020134228188</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5411140583554377</v>
+        <v>0.683311432325887</v>
       </c>
       <c r="G36" t="n">
-        <v>0.8067226890756303</v>
+        <v>0.8668823090320975</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2849162011173184</v>
+        <v>0.5726872246696035</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8047297942046504</v>
+        <v>0.8611833709723591</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1390386875646929</v>
+        <v>0.1162987174015005</v>
       </c>
       <c r="K36" t="n">
-        <v>204</v>
+        <v>520</v>
       </c>
       <c r="L36" t="n">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="M36" t="n">
-        <v>3552</v>
+        <v>3484</v>
       </c>
       <c r="N36" t="n">
-        <v>851</v>
+        <v>535</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2332,46 +2332,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.7900020916126334</v>
+        <v>0.8360175695461201</v>
       </c>
       <c r="B37" t="n">
-        <v>0.5702479338842975</v>
+        <v>0.6921985815602837</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1962085308056872</v>
+        <v>0.4625592417061611</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1962085308056872</v>
+        <v>0.4625592417061611</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9581320450885669</v>
+        <v>0.941760601180891</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5702479338842975</v>
+        <v>0.6921985815602837</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8080579447713898</v>
+        <v>0.8608930323846908</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2919605077574048</v>
+        <v>0.5545454545454546</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7882156385384629</v>
+        <v>0.8496116695031455</v>
       </c>
       <c r="J37" t="n">
-        <v>0.1417802526032854</v>
+        <v>0.1180320266730386</v>
       </c>
       <c r="K37" t="n">
-        <v>207</v>
+        <v>488</v>
       </c>
       <c r="L37" t="n">
-        <v>156</v>
+        <v>217</v>
       </c>
       <c r="M37" t="n">
-        <v>3570</v>
+        <v>3509</v>
       </c>
       <c r="N37" t="n">
-        <v>848</v>
+        <v>567</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2384,46 +2384,46 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.7949790794979079</v>
+        <v>0.8430962343096234</v>
       </c>
       <c r="B38" t="n">
-        <v>0.6022099447513812</v>
+        <v>0.7165242165242165</v>
       </c>
       <c r="C38" t="n">
-        <v>0.206831119544592</v>
+        <v>0.4772296015180266</v>
       </c>
       <c r="D38" t="n">
-        <v>0.206831119544592</v>
+        <v>0.4772296015180266</v>
       </c>
       <c r="E38" t="n">
-        <v>0.961352657004831</v>
+        <v>0.9465915190552872</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6022099447513812</v>
+        <v>0.7165242165242165</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8107741059302852</v>
+        <v>0.8648847474252085</v>
       </c>
       <c r="H38" t="n">
-        <v>0.307909604519774</v>
+        <v>0.5728929384965832</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8048737727910238</v>
+        <v>0.8626995185378707</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1384539883073773</v>
+        <v>0.1136780262960623</v>
       </c>
       <c r="K38" t="n">
-        <v>218</v>
+        <v>503</v>
       </c>
       <c r="L38" t="n">
-        <v>144</v>
+        <v>199</v>
       </c>
       <c r="M38" t="n">
-        <v>3582</v>
+        <v>3527</v>
       </c>
       <c r="N38" t="n">
-        <v>836</v>
+        <v>551</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2436,46 +2436,46 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.793305439330544</v>
+        <v>0.8462343096234309</v>
       </c>
       <c r="B39" t="n">
-        <v>0.59375</v>
+        <v>0.7140939597315437</v>
       </c>
       <c r="C39" t="n">
-        <v>0.198292220113852</v>
+        <v>0.5047438330170778</v>
       </c>
       <c r="D39" t="n">
-        <v>0.198292220113852</v>
+        <v>0.5047438330170778</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9616210413311863</v>
+        <v>0.9428341384863124</v>
       </c>
       <c r="F39" t="n">
-        <v>0.59375</v>
+        <v>0.7140939597315437</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8091689250225835</v>
+        <v>0.8706319702602231</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2972972972972973</v>
+        <v>0.5914396887159533</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7952082448479885</v>
+        <v>0.8517911216224061</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1405870680515418</v>
+        <v>0.1157590292184404</v>
       </c>
       <c r="K39" t="n">
-        <v>209</v>
+        <v>532</v>
       </c>
       <c r="L39" t="n">
-        <v>143</v>
+        <v>213</v>
       </c>
       <c r="M39" t="n">
-        <v>3583</v>
+        <v>3513</v>
       </c>
       <c r="N39" t="n">
-        <v>845</v>
+        <v>522</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2488,46 +2488,46 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.7968619246861924</v>
+        <v>0.840794979079498</v>
       </c>
       <c r="B40" t="n">
-        <v>0.610079575596817</v>
+        <v>0.6987788331071914</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2182163187855788</v>
+        <v>0.4886148007590133</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2182163187855788</v>
+        <v>0.4886148007590133</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9605475040257649</v>
+        <v>0.9404186795491143</v>
       </c>
       <c r="F40" t="n">
-        <v>0.610079575596817</v>
+        <v>0.6987788331071914</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8128548716784011</v>
+        <v>0.8666831560722236</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3214535290006988</v>
+        <v>0.5750977107761027</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7855839676268408</v>
+        <v>0.8531224759396253</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1424316273921587</v>
+        <v>0.1163891166310135</v>
       </c>
       <c r="K40" t="n">
-        <v>230</v>
+        <v>515</v>
       </c>
       <c r="L40" t="n">
-        <v>147</v>
+        <v>222</v>
       </c>
       <c r="M40" t="n">
-        <v>3579</v>
+        <v>3504</v>
       </c>
       <c r="N40" t="n">
-        <v>824</v>
+        <v>539</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2540,46 +2540,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.7855648535564853</v>
+        <v>0.8391213389121339</v>
       </c>
       <c r="B41" t="n">
-        <v>0.5396825396825397</v>
+        <v>0.6911764705882353</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1933649289099526</v>
+        <v>0.4900473933649289</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1933649289099526</v>
+        <v>0.4900473933649289</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9532885906040268</v>
+        <v>0.937986577181208</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5396825396825397</v>
+        <v>0.6911764705882353</v>
       </c>
       <c r="G41" t="n">
-        <v>0.8066787823716493</v>
+        <v>0.8665674603174603</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2847173761339846</v>
+        <v>0.5734886300610095</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8046654155666529</v>
+        <v>0.860766054899965</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1390579190127065</v>
+        <v>0.1164828050948029</v>
       </c>
       <c r="K41" t="n">
-        <v>204</v>
+        <v>517</v>
       </c>
       <c r="L41" t="n">
-        <v>174</v>
+        <v>231</v>
       </c>
       <c r="M41" t="n">
-        <v>3551</v>
+        <v>3494</v>
       </c>
       <c r="N41" t="n">
-        <v>851</v>
+        <v>538</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>

--- a/RESULTS/tables/internal_cv_fold_metrics.xlsx
+++ b/RESULTS/tables/internal_cv_fold_metrics.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,82 +417,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Sensitivity</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Specificity</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>PPV</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>NPV</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>AUROC</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Brier</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Fold</t>
         </is>
@@ -799,7 +787,7 @@
         <v>0.8529999262261094</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1172018836404627</v>
+        <v>0.1172018836426002</v>
       </c>
       <c r="K7" t="n">
         <v>493</v>
@@ -851,7 +839,7 @@
         <v>0.8626717634225266</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1131979235773683</v>
+        <v>0.1131979235808256</v>
       </c>
       <c r="K8" t="n">
         <v>512</v>
@@ -903,7 +891,7 @@
         <v>0.8536621728843217</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1150012531111617</v>
+        <v>0.1150012526707283</v>
       </c>
       <c r="K9" t="n">
         <v>537</v>
@@ -955,7 +943,7 @@
         <v>0.8559659747749289</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1155427984056087</v>
+        <v>0.1155427984056524</v>
       </c>
       <c r="K10" t="n">
         <v>528</v>
@@ -1004,10 +992,10 @@
         <v>0.5717463848720801</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8602036960463119</v>
+        <v>0.860203696046312</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1167256531419186</v>
+        <v>0.1167256531139676</v>
       </c>
       <c r="K11" t="n">
         <v>514</v>
@@ -1579,7 +1567,7 @@
         <v>0.8529999262261094</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1172018836404627</v>
+        <v>0.1172018836426002</v>
       </c>
       <c r="K22" t="n">
         <v>493</v>
@@ -1631,7 +1619,7 @@
         <v>0.8626717634225266</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1131979235773683</v>
+        <v>0.1131979235808256</v>
       </c>
       <c r="K23" t="n">
         <v>512</v>
@@ -1683,7 +1671,7 @@
         <v>0.8536621728843217</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1150012531111617</v>
+        <v>0.1150012526707283</v>
       </c>
       <c r="K24" t="n">
         <v>537</v>
@@ -1735,7 +1723,7 @@
         <v>0.8559659747749289</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1155427984056087</v>
+        <v>0.1155427984056524</v>
       </c>
       <c r="K25" t="n">
         <v>528</v>
@@ -1784,10 +1772,10 @@
         <v>0.5717463848720801</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8602036960463119</v>
+        <v>0.860203696046312</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1167256531419186</v>
+        <v>0.1167256531139676</v>
       </c>
       <c r="K26" t="n">
         <v>514</v>
@@ -1836,10 +1824,10 @@
         <v>0.5527065527065527</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8493224249732252</v>
+        <v>0.8493224249732251</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1181822722361692</v>
+        <v>0.1181822722361691</v>
       </c>
       <c r="K27" t="n">
         <v>485</v>
@@ -1891,7 +1879,7 @@
         <v>0.8624013420234853</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1138434331412837</v>
+        <v>0.1138434331412839</v>
       </c>
       <c r="K28" t="n">
         <v>503</v>
@@ -1943,7 +1931,7 @@
         <v>0.8515479460705377</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1158982461150199</v>
+        <v>0.1158982461150197</v>
       </c>
       <c r="K29" t="n">
         <v>529</v>
@@ -1995,7 +1983,7 @@
         <v>0.8527810116306664</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1165569484402106</v>
+        <v>0.1165569484402103</v>
       </c>
       <c r="K30" t="n">
         <v>515</v>
@@ -2047,7 +2035,7 @@
         <v>0.8602573873214797</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1166675693437824</v>
+        <v>0.1166675693437823</v>
       </c>
       <c r="K31" t="n">
         <v>514</v>
@@ -2099,7 +2087,7 @@
         <v>0.8499174495602821</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1178826463053576</v>
+        <v>0.1178826463053573</v>
       </c>
       <c r="K32" t="n">
         <v>489</v>
@@ -2151,7 +2139,7 @@
         <v>0.8630022784657991</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1135131156606892</v>
+        <v>0.1135131156606893</v>
       </c>
       <c r="K33" t="n">
         <v>507</v>
@@ -2307,7 +2295,7 @@
         <v>0.8611833709723591</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1162987174015005</v>
+        <v>0.1162987174015004</v>
       </c>
       <c r="K36" t="n">
         <v>520</v>
@@ -2356,10 +2344,10 @@
         <v>0.5545454545454546</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8496116695031455</v>
+        <v>0.8496116695031456</v>
       </c>
       <c r="J37" t="n">
-        <v>0.1180320266730386</v>
+        <v>0.1180320266730387</v>
       </c>
       <c r="K37" t="n">
         <v>488</v>
@@ -2411,7 +2399,7 @@
         <v>0.8626995185378707</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1136780262960623</v>
+        <v>0.1136780262960625</v>
       </c>
       <c r="K38" t="n">
         <v>503</v>
@@ -2463,7 +2451,7 @@
         <v>0.8517911216224061</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1157590292184404</v>
+        <v>0.1157590292184403</v>
       </c>
       <c r="K39" t="n">
         <v>532</v>
